--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J265"/>
+  <dimension ref="A1:J266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2734,30 +2734,82 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>gaz_edicola_due_santi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Edicola ai Due Santi</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>tabernacolo</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>41.761482099679</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>12.616871382457</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{
+  "type": "FeatureCollection",
+  "features": [
+    {
+      "type": "Feature",
+      "properties": {},
+      "geometry": {
+        "type": "Point",
+        "coordinates": [
+          12.616871382457,
+          41.761482099679
+        ]
+      }
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Posizione derivata da gaz_due_santi con uno scarto convenzionale di circa 40 m (+0,0003° lat/long), solo per distinguere i generatori della tassellazione: nessuna coordinata TCI disponibile. Esistenza del tabernacolo: piantina dei Castelli, TCI, Italia centrale IV (Manzotti 2010, p. 246).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>gaz_esquilino</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Esquilino</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Rione XV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>41.893298797354646</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>12.505248214532829</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2778,28 +2830,28 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>gaz_falcognana</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Falcognana</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>41.76433697008515</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>12.554930951232286</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2820,28 +2872,28 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Ferrovia Roma-Velletri</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>41.75795460249268</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>12.601126265148835</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2862,28 +2914,28 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>gaz_filettino</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Filettino</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>41.89068987779071</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>13.324876181760342</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2904,28 +2956,28 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>gaz_fiumicino</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Fiumicino</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>41.77328436591152</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>12.233541086841594</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2946,28 +2998,28 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>gaz_fontana_di_papa</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Fontana di Papa</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>41.68436279264858</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>12.651120729247085</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2988,38 +3040,38 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>gaz_fontanella_della_scrofa</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Fontanella della Scrofa</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>via della Scrofa</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Via dei Portoghesi, 00186</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>41.90164982576232</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>12.474936661874011</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3040,33 +3092,33 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>gaz_fontanella_di_borghese</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Fontanella di Borghese</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Via del Leoncino &amp;, Via della Fontanella di Borghese, 00186</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>41.90416313558839</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>12.478029650740126</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3087,38 +3139,38 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>gaz_foro_italico</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Foro Italico</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Foro Mussolini</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Viale del Foro Italico, 00135</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>41.93253953174582</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>12.457198145871402</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3139,33 +3191,33 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>gaz_forte_de_marmi</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Forte de' Marmi</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>43.959501773243005</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>10.168916830510229</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3186,28 +3238,28 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>gaz_frascati</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Frascati</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>41.80868282837834</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>12.676151782601927</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3228,33 +3280,33 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>gaz_frattocchie</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Frattocchie</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Frazione</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>41.766863233033725</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>12.616317604540413</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3275,33 +3327,33 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>gaz_galleria_colonna</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Galleria Colonna</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Via della Pilotta, 17, 00187</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>41.89761875811568</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>12.4847453656823</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3322,33 +3374,33 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>gaz_genova</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Genova</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>44.40813562461099</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>8.93119220339372</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3369,38 +3421,38 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>gaz_gianicolo</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Gianicolo</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Gianicolense</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Piazza di Sant'Onofrio, 00165</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>41.89772036230625</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>12.461430554962153</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3421,28 +3473,28 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>gaz_golfo_di_napoli</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Golfo di Napoli</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>40.70572169866826</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>14.148183487524973</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3463,28 +3515,28 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>gaz_grottaferrata</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Grottaferrata</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>41.79100156171508</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>12.670419992725682</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3505,28 +3557,28 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>gaz_india</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>21.55651170244903</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>78.74607895173585</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3547,43 +3599,43 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>gaz_istituto_dellenciclopedia_treccani</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Istituto dell'Enciclopedia Treccani</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Istituto Giovanni Treccani</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Palazzo Mattei, via Michelangelo Caetani (1925-1927), poi Palazzo Mattei, via di Paganica, 3-4</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Piazza della Enciclopedia Italiana, 4, 00186</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>41.89437602767189</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>12.477499531045336</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3604,28 +3656,28 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>gaz_ladispoli</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Ladispoli</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>41.95028305555387</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>12.078189603598291</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3646,33 +3698,33 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>gaz_largo_brancaccio</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Largo Brancaccio</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Largo Brancaccio</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>41.89499585680336</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>12.49962004376294</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3693,28 +3745,28 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>gaz_lazio</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>42.0974591857028</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>12.5184126891668</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3735,38 +3787,38 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>gaz_lungara</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Lungara</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>gaz_regina_coeli</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>via della Lungara</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>41.89549536697815</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>12.465430919268728</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3787,33 +3839,33 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>gaz_lungotevere_prati</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Lungotevere Prati</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Lungotevere di Prati</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>41.90488838494765</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>12.472885100933542</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3834,33 +3886,33 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>gaz_maccheronaro</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Maccheronaro</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>via del Gesù</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>41.89683405457504</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>12.478706693556006</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3881,28 +3933,28 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>gaz_marino</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Marino</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>41.77540942594233</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>12.66366867693179</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3923,28 +3975,28 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>gaz_marsica</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Marsica</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>41.9706811718908</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>13.6367770065667</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3965,33 +4017,33 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>gaz_milano</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Milano</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>45.46417984291975</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>9.188743384040578</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4012,28 +4064,28 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>gaz_molise</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Molise</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>41.667749</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>14.573358</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4054,33 +4106,33 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>gaz_molo_beverello</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Molo Beverello</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Molo del Porto di Napoli</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>40.83845747697102</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>14.25512089831604</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4101,33 +4153,33 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>gaz_monte_algido</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Monte Algido</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Colli Albani</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>41.75024597370798</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>12.774504127034607</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4148,33 +4200,33 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>gaz_monte_cengio</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Monte Cengio</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Monte dell'Altipiano Veneto</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>45.83464690564686</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>11.395</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4195,28 +4247,28 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>gaz_monte_circeo</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Monte Circeo</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>41.25277506832153</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>13.056903290988464</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4237,28 +4289,28 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>gaz_monte_manno</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Monte Manno</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>41.70507314535531</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>12.933066487462336</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4279,33 +4331,33 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>gaz_monte_matese</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Monte Matese</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Monte del Molise</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>41.451044369853264</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>14.366554255055233</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4326,28 +4378,28 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>gaz_monte_soratte</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Monte Soratte</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>42.27001081429104</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>12.490957672092293</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4368,33 +4420,33 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>gaz_monte_velino</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Monte Velino</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Monte tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>42.165421795541896</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>13.388224454942325</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4415,28 +4467,28 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>gaz_monteleone</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Monteleone Sabino</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>42.232609158947405</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>12.859136459324375</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4457,33 +4509,33 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>gaz_monti</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Monti</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Quartiere di Roma</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>41.89481897366331</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>12.49251620797544</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4504,33 +4556,33 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>gaz_monti_carseolani</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Monti Carseolani</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Catena montuosa tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>42.0749429984885</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>13.032114125147414</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4551,33 +4603,33 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>gaz_monti_ernici</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Monti Ernici</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Catena montuosa tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>41.81035580365862</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>13.48593067326618</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4598,33 +4650,33 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>gaz_monti_simbruini</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Monti Simbruini</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Catena montuosa tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>41.79718465634362</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>13.644952964344878</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4645,33 +4697,33 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>gaz_ostia</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Ostia</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>41.73245855250897</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>12.278829513185713</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4692,33 +4744,33 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>gaz_ovindoli</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Ovindoli</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Comune</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>42.13780481791833</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>13.51516522684632</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4739,28 +4791,28 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>gaz_padova</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>45.40750149300311</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>11.873753041768424</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4781,38 +4833,38 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>gaz_palazzo</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Palazzo</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Palazzo Morgana</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>00134 Stazione di Pavona-palazzo Morgana</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>41.71799629809183</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>12.597231861624314</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4833,33 +4885,33 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>gaz_palazzo_chigi</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Palazzo Chigi</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>P.za Colonna, 391, 00186</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>41.90123174971493</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>12.47981741059732</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4880,28 +4932,28 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>gaz_palazzo_della_immacolatella</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Palazzo della Immacolatella</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>40.84161917254697</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>14.258960456507776</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4922,33 +4974,33 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>gaz_palazzo_pio</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Palazzo Pio</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Piazza del Biscione</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>41.89533742794816</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>12.473007850337243</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4969,33 +5021,33 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>gaz_palazzo_ruspoli</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Palazzo Ruspoli</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Via della Fontanella di Borghese, 56, 00186 Roma RM</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>41.904291483212205</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>12.47872570766404</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5016,33 +5068,33 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>gaz_palazzo_simonetti</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Palazzo Simonetti</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Via Vittoria Colonna, 13, 00193</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>41.90520237070184</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>12.472392994101876</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5063,38 +5115,38 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>gaz_palazzo_venezia</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Palazzo Venezia</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>Palazzo del Mappamondo</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Piazza di Venezia, 3, 00186 Roma RM</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>41.89608880158758</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>12.482488256557962</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5115,28 +5167,28 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>gaz_palestrina</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Palestrina</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>41.83422291934301</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>12.888132917750513</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5157,38 +5209,38 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>gaz_pantheon</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Pantheon</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>Terme di Agrippa</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Piazza della Rotonda, 00186</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>41.89867683406545</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>12.476863407009992</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5209,33 +5261,33 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>gaz_pavona</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Pavona</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Pavona</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>41.72553775484286</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>12.61219280831608</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5256,33 +5308,33 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>gaz_piazza_colonna</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Piazza Colonna</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Piazza Colonna</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>41.90088848088894</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>12.47993539405843</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5303,33 +5355,33 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>gaz_piazza_di_pietra</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Piazza di Pietra</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Piazza di Pietra</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>41.89999819105845</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>12.479385384272035</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5350,33 +5402,33 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>gaz_piazza_di_spagna</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Piazza di Spagna</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Piazza di Spagna</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>41.90571279324034</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>12.482325564335817</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5397,38 +5449,38 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>gaz_piazza_esedra</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Piazza Esedra</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>Piazza della Repubblica</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Piazza Esedra</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>41.902472842408514</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>12.496321983673056</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5449,33 +5501,33 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>gaz_piazza_garibaldi</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Piazza Garibaldi</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Piazzale Giuseppe Garibaldi</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>41.89198953301559</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>12.460553558380496</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5496,38 +5548,38 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>gaz_piazza_montanara</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Piazza Montanara</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>Piazza Montanara</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>demolita nel 1934</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>41.89249955749</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>12.480250892538322</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5548,33 +5600,33 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>gaz_piazza_pollarola</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Piazza Pollarola</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Piazza Pollarola</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>41.895990126304326</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>12.472928812263008</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5595,38 +5647,38 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>gaz_piazza_rusticucci</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>Piazza Rusticucci</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>Piazza Rusticucci (demolita nel 1940)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Piazza Pio XII</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>41.90257061274494</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>12.45975825285214</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5647,33 +5699,33 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>gaz_piazza_san_giovanni</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Piazza San Giovanni</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Piazza San Giovanni in Laterano</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>41.88742084063378</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>12.506173147859243</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5694,33 +5746,33 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>gaz_piazza_san_lorenzo_in_lucina</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Piazza San Lorenzo in Lucina</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Piazza San Lorenzo in Lucina</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>41.90361766730038</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>12.47842775822113</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5741,33 +5793,33 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>gaz_piazza_san_pietro</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Piazza San Pietro</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Piazza San Pietro</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>41.9022608794283</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>12.457233173334089</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5788,33 +5840,33 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>gaz_piazza_verdi</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Piazza Verdi</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Piazza Giuseppe Verdi</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>41.919679006917015</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>12.495028075136045</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5835,33 +5887,33 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>gaz_piazza_vittorio_emanuele</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Piazza Vittorio Emanuele</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Piazza Vittorio Emanuele II</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>41.895124393144</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>12.5048427733034</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5882,28 +5934,28 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>gaz_piceno</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Piceno</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>42.85363261520004</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>13.567540016779384</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5924,33 +5976,33 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>gaz_pincio</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Pincio</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Colle del Pincio</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>41.9115148827888</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>12.479706623913264</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5971,38 +6023,38 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>gaz_policlinico</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>Policlinico</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Policlinico Umberto I</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Via Giovanni Maria Lancisi, 2, 00161</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>41.90863414049968</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>12.50917293969651</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6023,28 +6075,28 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>gaz_ponte_divino_amore</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Ponte al Divino Amore</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>41.76071420037528</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>12.599632278065911</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6065,38 +6117,38 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>gaz_porta_angelica</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Porta Angelica</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Porta Angelica</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>demolita nel 1888</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>41.90616185465161</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>12.456647366153756</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6117,33 +6169,33 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>gaz_porta_latina</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Porta Latina</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Mura aureliane, Via di Porta Latina, 14, 00179 Roma RM</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>41.8782334566828</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>12.499128817987987</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6164,33 +6216,33 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>gaz_porta_maggiore</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Porta Maggiore</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Piazza di Porta Maggiore, 00182 Roma RM</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>41.89143521467929</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>12.51518714724432</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6211,33 +6263,33 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>gaz_porta_pinciana</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Porta Pinciana</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Via Vittorio Veneto, 196, 00187</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>41.90968492139161</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>12.488262466067692</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6258,28 +6310,28 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>gaz_porta_san_paolo</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Porta San Paolo</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>41.87683414708175</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>12.481441271164153</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6300,33 +6352,33 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>gaz_pozzo_delle_cornacchie</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Pozzo delle Cornacchie</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>via del Pozzo delle Cornacchie</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>41.900132740766</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>12.476009448493592</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6347,33 +6399,33 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>gaz_prati</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Prati</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Rione XXII</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>41.90875142605531</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>12.465194747823828</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6394,28 +6446,28 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>gaz_prati_di_castello</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Prati di Castello</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>41.90963380954534</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>12.4651701137127</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6436,33 +6488,33 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>gaz_pratica_di_mare</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Pratica di Mare</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Pratica di Mare</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>41.66401971901388</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>12.479969808767637</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6483,28 +6535,28 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>gaz_predappio</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Predappio</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>44.10833194442195</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>11.981884102223214</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6525,38 +6577,38 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>gaz_publicii_clivio_de</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Publicii clivio de'</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>(clivio de')</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Clivio dei Publicii</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>41.88571995557534</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>12.48263328901126</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6577,28 +6629,28 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Quarto di Santa Fumia</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>41.73247489501876</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>12.58446168893847</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6619,33 +6671,33 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>gaz_quattro_cantoni</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Quattro Cantoni</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>via dei Quattro Cantoni, 00184</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>41.8964282361213</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>12.496553006621577</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6666,28 +6718,28 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>gaz_reggio_calabria</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Reggio Calabria</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>38.12747821699881</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>15.652447605612965</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6708,38 +6760,38 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>gaz_regina_coeli</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Regina Coeli</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>gaz_lungara</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Via della Lungara, 29, 00165</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>41.89541963959722</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>12.463486619911356</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6760,33 +6812,33 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>gaz_ripetta</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Ripetta</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Passeggiata di Ripetta</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>41.90910697941768</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>12.474356718309616</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6807,28 +6859,28 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>gaz_rocca_di_papa</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Rocca di Papa</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>41.76238950891051</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>12.706774730883602</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6849,28 +6901,28 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>gaz_rocca_orsina</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Rocca Orsina</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>41.76991636096222</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>12.658476221527655</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6891,33 +6943,33 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>gaz_rocca_savella</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Rocca Savella</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>clivo di Rocca Savella</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>41.88624438963685</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>12.48057907706965</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6938,28 +6990,28 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>gaz_roma</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Roma</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>41.89712290196547</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>12.483780073676602</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6980,33 +7032,33 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>gaz_sacro_cuore</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Sacro Cuore</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Via Marsala, 42, 00185</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>41.90255587411117</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>12.502382758820149</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7027,28 +7079,28 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>gaz_salsomaggiore</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Salsomaggiore</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>44.81905616432461</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>9.979392469787877</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7069,33 +7121,33 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>gaz_san_callisto</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>San Callisto</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>Via Appia Antica, 110/126, 00179</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>41.85910305676804</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>12.510725763767082</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7116,38 +7168,38 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>gaz_san_camillo</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>San Camillo</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>Ospedale Vannini dell'Istituto delle figlie di san Camillo</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Circonvallazione Gianicolense, 87, 00149</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>41.86966525125673</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>12.456303092017317</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7168,33 +7220,33 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>gaz_san_carlo_alle_quattro_fontane</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>San Carlo alle quattro fontane</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Via del Quirinale, 23, 00187</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>41.901863522116905</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>12.490746406108268</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7215,33 +7267,33 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>gaz_san_clemente</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>San Clemente</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Piazza di S. Clemente, 00184</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>41.88952632925135</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>12.497564978356351</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7262,38 +7314,38 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>gaz_san_giovanni</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>San Giovanni</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Commissariato di P.S. San Giovanni</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>via Casalmonferrato 25 00182, Roma</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>41.88075040110243</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>12.51886092484358</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7314,38 +7366,38 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>gaz_san_giovanni_in_laterano</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>San Giovanni in Laterano</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Galilei</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>P.za. San Giovanni In Laterano, 00184</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>41.88599013299084</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>12.50562195401995</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7366,38 +7418,38 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>gaz_san_lorenzo_al_verano</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>San Lorenzo al verano</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>San Lorenzo fuori le Mura</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Piazzale del Verano, 3, 00185</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>41.90261005150349</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>12.520581205893716</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7418,33 +7470,33 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>gaz_san_luigi_de_francesi</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>San Luigi de' Francesi</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Piazza di S. Luigi de' Francesi, 00186</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>41.899621753079465</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>12.47471902436365</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7465,33 +7517,33 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>gaz_san_martino_ai_monti</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>San Martino ai Monti</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Vle del Monte Oppio, 28, 00184</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>41.894677226531456</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>12.498384893656386</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7512,28 +7564,28 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>gaz_san_silvestro_in_capite</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>San Silvestro in Capite</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>41.90289491613001</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>12.4807727698506</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7554,28 +7606,28 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>gaz_sannio</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Sannio</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>41.260503</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>14.740775</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7596,33 +7648,33 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>gaz_santa_chiara</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>Santa Chiara</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>P.za di S. Chiara, 14, 00186</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>41.89767270494693</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>12.4766157816818</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7643,33 +7695,33 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>gaz_santa_croce_in_gerusalemme</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Santa Croce in Gerusalemme</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Piazza di S. Croce in Gerusalemme, 10, 00185</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>41.88898866930153</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>12.514682435189837</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7690,38 +7742,38 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>gaz_santa_margherita_in_abitacolo</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Santa Margherita in Abitacolo</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Santa Rita Invitàcolo</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Via Montanara, 00186</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>41.89267907132654</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>12.480113538487586</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7742,38 +7794,38 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>gaz_santa_maria_della_neve</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Santa Maria della Neve</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Santa Maria Maggiore</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Via del Colosseo, 19, 00184</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>41.89269599966251</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>12.490115463118764</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7794,33 +7846,33 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>gaz_santa_maria_in_aquiro</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Santa Maria in Aquiro</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Piazza Capranica, 00186</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>41.90014365391151</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>12.477999492672676</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7841,33 +7893,33 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>gaz_santa_maria_in_domnica</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Santa Maria in Dòmnica</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>Via della Navicella, 10, 00184</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>41.88479505138305</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>12.495713660513266</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7888,33 +7940,33 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>gaz_santa_maria_in_porta_paradisi</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Santa Maria in Porta Paradisi</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Via di Ripetta, 61, 00186</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>41.90753807576588</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>12.475955971957005</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7935,38 +7987,38 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>gaz_santa_maria_maggiore</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Santa Maria Maggiore</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Santa Maria della Neve</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>P.za di Santa Maria Maggiore, 00100</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>41.89783811990252</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>12.498397680304144</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7987,28 +8039,28 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>gaz_santa_maria_novella</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Santa Maria Novella</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>43.77709097635588</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>11.248280584031749</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8029,28 +8081,28 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>gaz_santa_maria_sopra_minerva</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Santa Maria sopra Minerva</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>41.89799121298735</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>12.477810026767758</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8071,33 +8123,33 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>gaz_santa_palomba</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Santa Palomba</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Via della Stazione, 00040</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>41.70649880109798</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>12.573826656277753</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I167" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8118,38 +8170,38 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>gaz_santa_rita_invitacolo</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Santa Rita Invitàcolo</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>Santa Margherita in Abitacolo</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Via Montanara, 00186</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>41.89267907132654</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H168" t="inlineStr">
         <is>
           <t>12.480113538487586</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I168" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8170,33 +8222,33 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>gaz_santagnese_in_agone</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Sant'Agnese in Agone</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Via di Santa Maria dell'Anima, 30/A, 00186</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>41.89886028109439</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>12.472549957571031</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8217,33 +8269,33 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>gaz_santagostino</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Sant'Agostino</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>P.za di S. Agostino, 00186</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>41.9008508106466</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H170" t="inlineStr">
         <is>
           <t>12.474278565476274</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8264,33 +8316,33 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>gaz_santandrea_della_valle</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Sant'Andrea della Valle</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>Corso Vittorio Emanuele II, 00186</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>41.89641220677437</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>12.474333258746212</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I171" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8311,33 +8363,33 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>gaz_santanna</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Sant'Anna</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Via Sant'Anna, 00120</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>41.90407297051054</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>12.457481602903693</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8358,33 +8410,33 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>gaz_santantonio_da_padova</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Sant'Antonio da Padova</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Via Merulana, 124, 00185</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>41.88896555883594</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>12.50405706965514</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8405,33 +8457,33 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>gaz_santi_quattro_coronati</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Santi Quattro Coronati</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>Via dei SS. Quattro, 20, 00184</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>41.88828469760136</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>12.498505681387911</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8452,38 +8504,38 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>gaz_santo_stefano_del_cacco_celio_santo_stefano</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Santo Stefano del Cacco, Celio-Santo Stefano</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>gaz_collegio_romano</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>via Santo Stefano del Cacco</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>41.89737347768524</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>12.47948307900791</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I175" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8504,33 +8556,33 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>gaz_santo_stefano_rotondo</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Santo Stefano Rotondo</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Via Santo Stefano Rotondo, 7, 00184</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>41.885983052252186</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H176" t="inlineStr">
         <is>
           <t>12.499315306942016</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I176" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8551,28 +8603,28 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>gaz_sardegna</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Sardegna</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>40.23470155220895</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>9.054925146792344</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I177" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8593,28 +8645,28 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>gaz_sassari</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Sassari</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>40.72924779449954</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>8.55541661770075</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8635,38 +8687,38 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>gaz_solforata</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Solforata</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Solfarata, Solfatara</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Solfarata</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>41.70161467494166</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>12.538157750574666</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I179" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8687,28 +8739,28 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>gaz_soriano_nel_cimino</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Soriano nel Cimino</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>42.43655912777748</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>12.235774006217756</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I180" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8729,33 +8781,33 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>gaz_suburra</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Suburra</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Suburra, Roma</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>41.89676284011875</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>12.49666104629743</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I181" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8776,38 +8828,38 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>gaz_teatro_jovinelli</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Teatro Jovinelli</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>Ambra Jovinelli</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Via Guglielmo Pepe, 45, 00185</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>41.89552360992579</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="H182" t="inlineStr">
         <is>
           <t>12.508280896240649</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="I182" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8828,38 +8880,38 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>gaz_tempio_di_agrippa</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Tempio di Agrippa</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>Pantheon</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>Piazza della Rotonda, 00186</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>41.89867683406545</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H183" t="inlineStr">
         <is>
           <t>12.476863407009992</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I183" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8880,33 +8932,33 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>gaz_terme_di_caracalla</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Terme di Caracalla</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Viale delle Terme di Caracalla, 00153</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>41.87937370424267</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>12.492407213493443</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I184" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8927,33 +8979,33 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>gaz_termini</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Termini</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Via Giovanni Giolitti, 40, 00185</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>41.90058242591175</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>12.502530478441573</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I185" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8974,33 +9026,33 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>gaz_terracina</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Terracina</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Comune</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>41.29047601665066</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="H186" t="inlineStr">
         <is>
           <t>13.249936342430493</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I186" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9021,33 +9073,33 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>gaz_tevere</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Tevere</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Fiume</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>41.89465722886191</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>12.467929197570816</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I187" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9068,28 +9120,28 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>gaz_tivoli</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Tivoli</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>41.95975597738329</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
+      <c r="H188" t="inlineStr">
         <is>
           <t>12.802413747816448</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I188" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9110,43 +9162,43 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>gaz_tor_ser_paolo</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Tor Ser Paolo</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>Torre Messer Paoli</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>Tor Ser Paolo</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Ciampino (Colli Albani)</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="G189" t="inlineStr">
         <is>
           <t>41.77489532732517</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="H189" t="inlineStr">
         <is>
           <t>12.626476138456598</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="I189" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9167,33 +9219,33 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>gaz_torraccio</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Torraccio</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Frazione di Marino</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>41.760346741901486</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
+      <c r="H190" t="inlineStr">
         <is>
           <t>12.623648121781372</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="I190" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9214,33 +9266,33 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>gaz_traforo</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>Traforo</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>Traforo Umberto I</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>41.90087528377779</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
+      <c r="H191" t="inlineStr">
         <is>
           <t>12.48796567063664</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I191" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9261,28 +9313,28 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>gaz_trastevere</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>Trastevere</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>41.88539020297163</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
+      <c r="H192" t="inlineStr">
         <is>
           <t>12.47032722280828</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
+      <c r="I192" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9303,33 +9355,33 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>gaz_tranvie_dei_castelli</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>Tranvie dei Castelli</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>Tramvie dei Castelli</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>41.87842995242856</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H193" t="inlineStr">
         <is>
           <t>12.518773149025854</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
+      <c r="I193" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9350,33 +9402,33 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>gaz_vado_ligure</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>Vado Ligure</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>44.27104046105365</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H194" t="inlineStr">
         <is>
           <t>8.43855565508531</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I194" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9397,33 +9449,33 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>gaz_valle_fondo</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Valle Fondo</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>41.72754639015884</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H195" t="inlineStr">
         <is>
           <t>12.649994748861523</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I195" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9444,33 +9496,33 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>gaz_velletri</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>Velletri</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Comune</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G196" t="inlineStr">
         <is>
           <t>41.68473269013517</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="H196" t="inlineStr">
         <is>
           <t>12.777920637406812</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I196" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9491,33 +9543,33 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>gaz_verona</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>45.44286986165943</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
+      <c r="H197" t="inlineStr">
         <is>
           <t>10.998439464162914</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I197" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9538,33 +9590,33 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>gaz_via_anziate</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>Via Anziate</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>Anziatina, Nettunense</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>41.91177548861766</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="H198" t="inlineStr">
         <is>
           <t>12.442903033569449</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I198" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9585,28 +9637,28 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>gaz_via_appia</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Via Appia</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>41.85054042792461</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
+      <c r="H199" t="inlineStr">
         <is>
           <t>12.52314794887518</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
+      <c r="I199" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9627,28 +9679,28 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>gaz_via_ardeatina</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Via Ardeatina</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>41.748548036845285</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
+      <c r="H200" t="inlineStr">
         <is>
           <t>12.560749021883575</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I200" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9669,28 +9721,28 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>gaz_via_boncompagni</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>Via Boncompagni</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G201" t="inlineStr">
         <is>
           <t>41.908587241676514</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
+      <c r="H201" t="inlineStr">
         <is>
           <t>12.49349032119079</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
+      <c r="I201" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9711,33 +9763,33 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>gaz_via_botteghe_oscure</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>Via Botteghe Oscure</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>via delle Botteghe Oscure</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>41.89509493955358</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
+      <c r="H202" t="inlineStr">
         <is>
           <t>12.478981335522056</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I202" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9758,33 +9810,33 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>gaz_via_campo_marzio</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>Via Campo Marzio</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>via di Campo Marzio</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>41.90233603425503</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H203" t="inlineStr">
         <is>
           <t>12.477565835193412</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I203" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9805,28 +9857,28 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>gaz_via_capo_dafrica</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Via Capo d'Africa</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>41.888955504808656</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
+      <c r="H204" t="inlineStr">
         <is>
           <t>12.495370807914474</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I204" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9847,28 +9899,28 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>gaz_via_carlo_alberto</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Via Carlo Alberto</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>41.89631462157369</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H205" t="inlineStr">
         <is>
           <t>12.501608522565736</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I205" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9889,28 +9941,28 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>gaz_via_colonna_vittoria</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Via Colonna Vittoria</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>41.90532009591583</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H206" t="inlineStr">
         <is>
           <t>12.472080293657111</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I206" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9931,28 +9983,28 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>gaz_via_dazeglio</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Via D'Azeglio</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>41.9005646386736</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H207" t="inlineStr">
         <is>
           <t>12.497986264095715</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I207" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9973,28 +10025,28 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>gaz_via_de_merli</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>Via de' Merli</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>41.8919173419505</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H208" t="inlineStr">
         <is>
           <t>12.50204620435122</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I208" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10015,28 +10067,28 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>gaz_via_de_querceti</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>Via de' Querceti</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>41.88826403566792</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H209" t="inlineStr">
         <is>
           <t>12.497769533571477</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I209" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10057,28 +10109,28 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>gaz_via_degli_zingari</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Via degli Zingari</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>41.8953237669349</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>12.491807177069209</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I210" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10099,28 +10151,28 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>gaz_via_dei_banchi_vecchi</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>Via dei Banchi Vecchi</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>41.89855410311026</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>12.466855862738894</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I211" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10141,28 +10193,28 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>gaz_via_dei_capocci</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>Via dei Capocci</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>41.89635704216215</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H212" t="inlineStr">
         <is>
           <t>12.493746031107008</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I212" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10183,28 +10235,28 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>gaz_via_dei_fienili</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Via dei Fienili</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>41.89082656400838</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="H213" t="inlineStr">
         <is>
           <t>12.48348109299745</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
+      <c r="I213" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10225,28 +10277,28 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>gaz_via_dei_greci</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Via dei Greci</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>41.907686875920895</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
+      <c r="H214" t="inlineStr">
         <is>
           <t>12.478760733837431</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
+      <c r="I214" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10267,28 +10319,28 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>gaz_via_dei_serpenti</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>Via dei Serpenti</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>41.89625372175469</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
+      <c r="H215" t="inlineStr">
         <is>
           <t>12.490298122566564</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
+      <c r="I215" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10309,28 +10361,28 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>gaz_via_del_corso</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>Via del Corso</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>41.90038661195777</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
+      <c r="H216" t="inlineStr">
         <is>
           <t>12.480692510904577</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
+      <c r="I216" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10351,28 +10403,28 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>gaz_via_del_gesu</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Via del Gesù</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G217" t="inlineStr">
         <is>
           <t>41.8967983204413</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
+      <c r="H217" t="inlineStr">
         <is>
           <t>12.478768993659564</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
+      <c r="I217" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10393,33 +10445,33 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>gaz_via_del_gobbo</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>Via del Gobbo</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>Via Aurelio del Gobbo</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>41.77631176902448</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H218" t="inlineStr">
         <is>
           <t>12.67390716539034</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I218" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10440,28 +10492,28 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>gaz_via_del_parlamento</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Via del Parlamento</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G219" t="inlineStr">
         <is>
           <t>41.90266671761795</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="H219" t="inlineStr">
         <is>
           <t>12.479531435421766</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I219" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10482,28 +10534,28 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>gaz_via_della_caffarella</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Via della Caffarella</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G220" t="inlineStr">
         <is>
           <t>41.86491462396609</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H220" t="inlineStr">
         <is>
           <t>12.51298416209954</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I220" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10524,28 +10576,28 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>gaz_via_della_falcognana</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Via della Falcognana</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>41.75989937203588</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H221" t="inlineStr">
         <is>
           <t>12.58052436788742</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="I221" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10566,28 +10618,28 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>gaz_via_della_navicella</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Via della Navicella</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G222" t="inlineStr">
         <is>
           <t>41.883995357992056</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H222" t="inlineStr">
         <is>
           <t>12.496271259883107</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I222" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10608,28 +10660,28 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>gaz_via_della_palombella</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>Via della Palombella</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>41.89835257325988</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="H223" t="inlineStr">
         <is>
           <t>12.476684905643626</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="I223" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10650,28 +10702,28 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>gaz_via_della_scrofa</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>Via della Scrofa</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G224" t="inlineStr">
         <is>
           <t>41.89999474967304</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H224" t="inlineStr">
         <is>
           <t>12.477970515691876</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I224" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10692,28 +10744,28 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>gaz_via_della_vite</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>Via della Vite</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G225" t="inlineStr">
         <is>
           <t>41.90388247365601</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
+      <c r="H225" t="inlineStr">
         <is>
           <t>12.481236040688875</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
+      <c r="I225" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10734,28 +10786,28 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>gaz_via_delle_coppelle</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>Via delle Coppelle</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G226" t="inlineStr">
         <is>
           <t>41.900528326072674</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="H226" t="inlineStr">
         <is>
           <t>12.475815197103683</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
+      <c r="I226" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10776,33 +10828,33 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>gaz_via_di_ferro</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>Via di Ferro</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>via Capo di Ferro</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G227" t="inlineStr">
         <is>
           <t>41.89411186215077</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
+      <c r="H227" t="inlineStr">
         <is>
           <t>12.47225542803289</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
+      <c r="I227" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10823,28 +10875,28 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>gaz_via_di_grotta_pinta</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>Via di Grotta Pinta</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G228" t="inlineStr">
         <is>
           <t>41.895285483518485</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>12.473999194642012</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
+      <c r="I228" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10865,28 +10917,28 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>gaz_via_di_pietra</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>Via di Pietra</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G229" t="inlineStr">
         <is>
           <t>41.90017316845467</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
+      <c r="H229" t="inlineStr">
         <is>
           <t>12.480302763446346</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
+      <c r="I229" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10907,28 +10959,28 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>gaz_via_di_san_paolo_della_croce</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>Via di San Paolo della Croce</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>41.88609007715952</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>12.494225506290569</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
+      <c r="I230" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10949,28 +11001,28 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>gaz_via_di_santo_stefano_rotondo</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>Via di Santo Stefano Rotondo</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G231" t="inlineStr">
         <is>
           <t>41.8859031777105</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="H231" t="inlineStr">
         <is>
           <t>12.49934749037454</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
+      <c r="I231" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10991,28 +11043,28 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>gaz_via_frangipane</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>Via Frangipane</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G232" t="inlineStr">
         <is>
           <t>41.89345109820309</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
+      <c r="H232" t="inlineStr">
         <is>
           <t>12.490184834220564</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="I232" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11033,38 +11085,38 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>gaz_via_labbricana</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>Via Labbricana</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>via Labicana</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>via Labicana</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>41.88997394077698</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H233" t="inlineStr">
         <is>
           <t>12.498761606943075</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I233" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11085,33 +11137,33 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>gaz_via_lanza</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>Via Lanza</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>via Giovanni Lanza</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G234" t="inlineStr">
         <is>
           <t>41.8952468123314</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
+      <c r="H234" t="inlineStr">
         <is>
           <t>12.496558649455126</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
+      <c r="I234" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11132,28 +11184,28 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>gaz_via_ludovisi</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>Via Ludovisi</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>41.907046946215466</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
+      <c r="H235" t="inlineStr">
         <is>
           <t>12.487880279008024</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="I235" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11174,28 +11226,28 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>gaz_via_mamiani</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>Via Mamiani</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G236" t="inlineStr">
         <is>
           <t>41.8962647321153</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
+      <c r="H236" t="inlineStr">
         <is>
           <t>12.505176649501491</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="I236" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11216,28 +11268,28 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>gaz_via_massimo_dazeglio</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>Via Massimo d'Azeglio</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G237" t="inlineStr">
         <is>
           <t>41.7708010201672</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
+      <c r="H237" t="inlineStr">
         <is>
           <t>12.656666611845928</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="I237" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11258,28 +11310,28 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>gaz_via_merulana</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>Via Merulana</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G238" t="inlineStr">
         <is>
           <t>41.8919173419505</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
+      <c r="H238" t="inlineStr">
         <is>
           <t>12.50204620435122</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
+      <c r="I238" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11300,28 +11352,28 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>gaz_via_milano</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>Via Milano</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G239" t="inlineStr">
         <is>
           <t>41.89826988439785</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
+      <c r="H239" t="inlineStr">
         <is>
           <t>12.490991532899102</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
+      <c r="I239" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11342,33 +11394,33 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>gaz_via_monte_caprino</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>Via Monte Caprino</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>via di Monte Caprino</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G240" t="inlineStr">
         <is>
           <t>41.8915647770543</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
+      <c r="H240" t="inlineStr">
         <is>
           <t>12.481163670442754</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="I240" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11389,28 +11441,28 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>gaz_via_montebello</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>Via Montebello</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G241" t="inlineStr">
         <is>
           <t>41.90645672391186</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
+      <c r="H241" t="inlineStr">
         <is>
           <t>12.501167377390898</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
+      <c r="I241" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11431,28 +11483,28 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>gaz_via_nicotera</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>Via Nicotera</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>41.91624918540069</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
+      <c r="H242" t="inlineStr">
         <is>
           <t>12.468244588924025</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
+      <c r="I242" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11473,28 +11525,28 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>gaz_via_orazio</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>Via Orazio</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G243" t="inlineStr">
         <is>
           <t>41.9159462938855</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
+      <c r="H243" t="inlineStr">
         <is>
           <t>12.468458865543028</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
+      <c r="I243" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11515,28 +11567,28 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>gaz_via_panisperna</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>Via Panisperna</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G244" t="inlineStr">
         <is>
           <t>41.89663706340232</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
+      <c r="H244" t="inlineStr">
         <is>
           <t>12.491129905973104</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
+      <c r="I244" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11557,33 +11609,33 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>gaz_via_popolonia</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>Via Popolonia</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>Via populonia</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="G245" t="inlineStr">
         <is>
           <t>41.8764745142944</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
+      <c r="H245" t="inlineStr">
         <is>
           <t>12.50579364816932</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
+      <c r="I245" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11604,28 +11656,28 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>gaz_via_ricasoli</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>Via Ricasoli</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G246" t="inlineStr">
         <is>
           <t>41.89558786458463</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
+      <c r="H246" t="inlineStr">
         <is>
           <t>12.50606607937935</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
+      <c r="I246" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11646,28 +11698,28 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>gaz_via_valadier</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>Via Valadier</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G247" t="inlineStr">
         <is>
           <t>41.90825496417197</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
+      <c r="H247" t="inlineStr">
         <is>
           <t>12.469020520920948</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
+      <c r="I247" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11688,28 +11740,28 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>gaz_via_veneto</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>Via Veneto</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G248" t="inlineStr">
         <is>
           <t>41.906261368657</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>12.48958462091846</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
+      <c r="I248" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11730,28 +11782,28 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>gaz_via_venti_settembre</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>Via Venti Settembre</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="G249" t="inlineStr">
         <is>
           <t>41.90577385586054</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H249" t="inlineStr">
         <is>
           <t>12.496004176747949</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
+      <c r="I249" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11772,28 +11824,28 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>gaz_via_villari</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>Via Vìllari</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G250" t="inlineStr">
         <is>
           <t>41.88999351453406</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
+      <c r="H250" t="inlineStr">
         <is>
           <t>12.502061807590628</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
+      <c r="I250" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11814,28 +11866,28 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>gaz_via_zanardelli</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>Via Zanardelli</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G251" t="inlineStr">
         <is>
           <t>41.9012714375299</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
+      <c r="H251" t="inlineStr">
         <is>
           <t>12.472265477389731</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
+      <c r="I251" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11856,38 +11908,38 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>gaz_viale_della_regina</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>Viale della Regina</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>vedi anche Viale Regina Margherita</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F252" t="inlineStr">
         <is>
           <t>viale Regina Margherita</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G252" t="inlineStr">
         <is>
           <t>41.914435250731664</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
+      <c r="H252" t="inlineStr">
         <is>
           <t>12.505081063122308</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
+      <c r="I252" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11908,28 +11960,28 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>gaz_viale_liegi</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>Viale Liegi</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>41.92139386789227</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
+      <c r="H253" t="inlineStr">
         <is>
           <t>12.495723748817309</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
+      <c r="I253" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11950,33 +12002,33 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>gaz_viale_regina_margherita</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>Viale Regina Margherita</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>vedi anche Viale della Regina</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="G254" t="inlineStr">
         <is>
           <t>41.914435250731664</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
+      <c r="H254" t="inlineStr">
         <is>
           <t>12.505081063122308</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr">
+      <c r="I254" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11997,33 +12049,33 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>gaz_vicenza</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Vicenza</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F255" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
+      <c r="G255" t="inlineStr">
         <is>
           <t>45.54782811997265</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H255" t="inlineStr">
         <is>
           <t>11.54666863709906</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
+      <c r="I255" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12044,33 +12096,33 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>gaz_vicolo_ciancaleoni</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Vicolo Ciancaleoni</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>vicolo de' Ciancaleoni</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G256" t="inlineStr">
         <is>
           <t>41.89652544879445</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
+      <c r="H256" t="inlineStr">
         <is>
           <t>12.49319562190167</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
+      <c r="I256" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12091,33 +12143,33 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>gaz_vicolo_della_bucimazza</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>Vicolo della Bucimazza</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>via Bucimazza</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
+      <c r="G257" t="inlineStr">
         <is>
           <t>41.89085398497711</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
+      <c r="H257" t="inlineStr">
         <is>
           <t>12.48282256606494</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr">
+      <c r="I257" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12138,28 +12190,28 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>gaz_vicolo_delle_grotte_del_teatro</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Vicolo delle Grotte del Teatro</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G258" t="inlineStr">
         <is>
           <t>41.89461101972113</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
+      <c r="H258" t="inlineStr">
         <is>
           <t>12.47247006996503</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
+      <c r="I258" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12180,28 +12232,28 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>gaz_villa_borghese</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Villa Borghese</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G259" t="inlineStr">
         <is>
           <t>41.91403582418124</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
+      <c r="H259" t="inlineStr">
         <is>
           <t>12.485398757632616</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
+      <c r="I259" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12222,28 +12274,28 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>gaz_villa_celimontana</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Villa Celimontana</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G260" t="inlineStr">
         <is>
           <t>41.88404468598669</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H260" t="inlineStr">
         <is>
           <t>12.495211796641748</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
+      <c r="I260" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12264,28 +12316,28 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>gaz_villa_deste</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Villa d'Este</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G261" t="inlineStr">
         <is>
           <t>41.96358343762597</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H261" t="inlineStr">
         <is>
           <t>12.795864786733311</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
+      <c r="I261" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12306,28 +12358,28 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>gaz_villa_gregoriana</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Villa Gregoriana</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G262" t="inlineStr">
         <is>
           <t>41.96553240632673</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H262" t="inlineStr">
         <is>
           <t>12.801778925481416</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
+      <c r="I262" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12348,28 +12400,28 @@
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>gaz_viminale</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Viminale</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G263" t="inlineStr">
         <is>
           <t>41.89805973978667</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H263" t="inlineStr">
         <is>
           <t>12.494448968864743</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
+      <c r="I263" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12390,28 +12442,28 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>gaz_vinchiaturo</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Vinchiaturo</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G264" t="inlineStr">
         <is>
           <t>41.49401046795862</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H264" t="inlineStr">
         <is>
           <t>14.587203598469978</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
+      <c r="I264" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12432,28 +12484,28 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>gaz_vomero</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>Vomero</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G265" t="inlineStr">
         <is>
           <t>40.84468964152708</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H265" t="inlineStr">
         <is>
           <t>14.23166148030254</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
+      <c r="I265" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12474,28 +12526,28 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>gaz_zagarolo</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>Zagarolo</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="G266" t="inlineStr">
         <is>
           <t>41.839732856050645</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
+      <c r="H266" t="inlineStr">
         <is>
           <t>12.829976839865571</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr">
+      <c r="I266" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",

--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -5071,12 +5071,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>gaz_palazzo_simonetti</t>
+          <t>gaz_palazzo_odescalchi_simonetti</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Palazzo Simonetti</t>
+          <t>Palazzo Odescalchi Simonetti</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5112,6 +5112,11 @@
     }
   ]
 }</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Candidato della lettura di Terzoli (cit. in Pinotti 2025, p. 78): palazzo Odescalchi Simonetti, già pensione White, dove Gadda aveva abitato. Civico 11 secondo Pinotti; il dato precedente indicava 13. Non è il referente di palazzo_simonetti: entità predisposta per l'identificazione attribuita.</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J266"/>
+  <dimension ref="A1:J267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,25 +1819,82 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>gaz_casale_abbruciato</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Casale Abbruciato</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Casal Bruciato; Casale Abbrusciato; Casale Bruciato</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Casale dell'Agro romano a sud di Roma (Nibby, Dintorni di Roma, p. 569)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>41.7335</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>12.583</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{
+  "type": "FeatureCollection",
+  "features": [
+    {
+      "type": "Feature",
+      "properties": {},
+      "geometry": {
+        "type": "Point",
+        "coordinates": [
+          12.583,
+          41.7335
+        ]
+      }
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Posizione ADOTTATA: TCI, Italia centrale I, carta «Colli Laziali, Monti Lepini ed Ernici» 1:250.000, inserita tra le pp. 480 e 481 (Manzotti 2010, Tav. VI, p. 300): casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato. Coordinate stimate (precisione ~1 km): punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia (OpenStreetMap). Posizione ALTERNATIVA: IGM, F. 150 III SO, 1:25.000, rilievo 1872, aggiornamenti 1931 e 1940 (Manzotti 2010, Tav. VII, p. 301): «Casale Abbruciato» a ovest della Roma–Napoli, stimato a 41.7168 N 12.5683 E (reticolo UTM 33 della tavola, E 297,7 N 4621,3 km; precisione ~250 m). Manzotti 2010, pp. 268–269. Nella nota Manzotti rinvia alle tavole come «V» e «VI»: qui si citano secondo le didascalie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>gaz_castelli_romani</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Castelli Romani</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>41.76583589207368</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>12.708345346043885</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -1858,28 +1915,28 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>gaz_castel_di_leva</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Castel di Leva</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>41.7788626363677</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>12.504796743330868</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -1900,33 +1957,33 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>gaz_castel_gandolfo</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Castel Gandolfo</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>gaz_castello</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>41.75005641875434</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>12.64847290122697</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -1947,28 +2004,28 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>gaz_castel_porziano</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Castel Porziano</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>41.74517216671914</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>12.400109186081606</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -1989,28 +2046,28 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>gaz_castel_savello</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Castel Savello</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>41.72761786263662</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>12.639910072691912</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2031,33 +2088,33 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>gaz_castello</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Castello</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>gaz_castel_gandolfo</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>41.75143747946607</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>12.648544024883735</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2078,33 +2135,33 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>gaz_cecchina</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Cecchina</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Cecchina</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>41.69302437483999</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>12.649648693210247</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2125,33 +2182,33 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>gaz_celio</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Celio</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Rione XIX</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>41.88727982359032</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>12.497441089867236</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2172,38 +2229,38 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>gaz_centrale_del_latte</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Centrale del Latte</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Società Italiana di Alimentazione</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>via Giolitti</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>41.8959248058548</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>12.507267048053844</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2224,33 +2281,33 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>gaz_ciampino</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Ciampino</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Ciampino</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>41.80425628012242</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>12.599503897985612</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2271,28 +2328,28 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>gaz_civitavecchia</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Civitavecchia</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>42.09490840988426</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>11.796544699426349</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2313,38 +2370,38 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>gaz_collegio_romano</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Collegio Romano</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>gaz_santo_stefano_del_cacco_celio_santo_stefano</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>via Santo Stefano del Cacco</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>41.89737347768524</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>12.47948307900791</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2365,28 +2422,28 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>gaz_colli_albani</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Colli Albani</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>41.7320873</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>12.6960074</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2407,38 +2464,38 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>gaz_colosseo</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Colosseo</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Colisèo, Culiseo</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Piazza del Colosseo, 1, 00184</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>41.89035225098585</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>12.49219290392497</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2459,38 +2516,38 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>gaz_corso_umberto</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Corso Umberto</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Corso Umberto I</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>via del Corso</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>41.90323194218181</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>12.479507636411158</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2511,33 +2568,33 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>gaz_dazeglio</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>D'Azeglio</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Via Cavour, 18, 00185</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>41.90013088374668</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>12.49926878303822</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2558,28 +2615,28 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>gaz_direttissima_roma_napoli</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Direttissima Roma-Napoli</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>41.64771889912876</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>12.64899568499919</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2600,28 +2657,28 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>gaz_divino_amore</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Divino Amore</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>41.777158165633374</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>12.546337915729302</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2642,33 +2699,33 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>gaz_dosso_faiti</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Dosso Faiti</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Collina nel Carso</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>45.884990244121546</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>13.649815236363924</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2689,28 +2746,28 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>gaz_due_santi</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Due Santi</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>41.76118209967858</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>12.616571382457442</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2731,33 +2788,33 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>gaz_edicola_due_santi</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Edicola ai Due Santi</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>tabernacolo</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>41.761482099679</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>12.616871382457</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2777,39 +2834,39 @@
 }</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Posizione derivata da gaz_due_santi con uno scarto convenzionale di circa 40 m (+0,0003° lat/long), solo per distinguere i generatori della tassellazione: nessuna coordinata TCI disponibile. Esistenza del tabernacolo: piantina dei Castelli, TCI, Italia centrale IV (Manzotti 2010, p. 246).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>gaz_esquilino</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Esquilino</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Rione XV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>41.893298797354646</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>12.505248214532829</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2830,28 +2887,28 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>gaz_falcognana</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Falcognana</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>41.76433697008515</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>12.554930951232286</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2872,28 +2929,28 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Ferrovia Roma-Velletri</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>41.75795460249268</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>12.601126265148835</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2914,28 +2971,28 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>gaz_filettino</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Filettino</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>41.89068987779071</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>13.324876181760342</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2956,28 +3013,28 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>gaz_fiumicino</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Fiumicino</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>41.77328436591152</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>12.233541086841594</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -2998,28 +3055,28 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>gaz_fontana_di_papa</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Fontana di Papa</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>41.68436279264858</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>12.651120729247085</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3040,38 +3097,38 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>gaz_fontanella_della_scrofa</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Fontanella della Scrofa</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>via della Scrofa</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Via dei Portoghesi, 00186</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>41.90164982576232</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>12.474936661874011</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3092,33 +3149,33 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>gaz_fontanella_di_borghese</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Fontanella di Borghese</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Via del Leoncino &amp;, Via della Fontanella di Borghese, 00186</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>41.90416313558839</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>12.478029650740126</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3139,38 +3196,38 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>gaz_foro_italico</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Foro Italico</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Foro Mussolini</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Viale del Foro Italico, 00135</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>41.93253953174582</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>12.457198145871402</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3191,33 +3248,33 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>gaz_forte_de_marmi</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Forte de' Marmi</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>43.959501773243005</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>10.168916830510229</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3238,28 +3295,28 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>gaz_frascati</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Frascati</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>41.80868282837834</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>12.676151782601927</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3280,33 +3337,33 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>gaz_frattocchie</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Frattocchie</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Frazione</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>41.766863233033725</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>12.616317604540413</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3327,33 +3384,33 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>gaz_galleria_colonna</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Galleria Colonna</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Via della Pilotta, 17, 00187</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>41.89761875811568</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>12.4847453656823</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3374,33 +3431,33 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>gaz_genova</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Genova</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>44.40813562461099</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>8.93119220339372</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3421,38 +3478,38 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>gaz_gianicolo</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Gianicolo</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Gianicolense</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Piazza di Sant'Onofrio, 00165</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>41.89772036230625</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>12.461430554962153</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3473,28 +3530,28 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>gaz_golfo_di_napoli</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Golfo di Napoli</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>40.70572169866826</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>14.148183487524973</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3515,28 +3572,28 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>gaz_grottaferrata</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Grottaferrata</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>41.79100156171508</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>12.670419992725682</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3557,28 +3614,28 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>gaz_india</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>21.55651170244903</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>78.74607895173585</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3599,43 +3656,43 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>gaz_istituto_dellenciclopedia_treccani</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Istituto dell'Enciclopedia Treccani</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Istituto Giovanni Treccani</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Palazzo Mattei, via Michelangelo Caetani (1925-1927), poi Palazzo Mattei, via di Paganica, 3-4</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Piazza della Enciclopedia Italiana, 4, 00186</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>41.89437602767189</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>12.477499531045336</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3656,28 +3713,28 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>gaz_ladispoli</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Ladispoli</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>41.95028305555387</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>12.078189603598291</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3698,33 +3755,33 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>gaz_largo_brancaccio</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Largo Brancaccio</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Largo Brancaccio</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>41.89499585680336</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>12.49962004376294</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3745,28 +3802,28 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>gaz_lazio</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>42.0974591857028</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>12.5184126891668</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3787,38 +3844,38 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>gaz_lungara</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Lungara</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>gaz_regina_coeli</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>via della Lungara</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>41.89549536697815</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>12.465430919268728</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3839,33 +3896,33 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>gaz_lungotevere_prati</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Lungotevere Prati</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Lungotevere di Prati</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>41.90488838494765</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>12.472885100933542</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3886,33 +3943,33 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>gaz_maccheronaro</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Maccheronaro</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>via del Gesù</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>41.89683405457504</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>12.478706693556006</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3933,28 +3990,28 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>gaz_marino</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Marino</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>41.77540942594233</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>12.66366867693179</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -3975,28 +4032,28 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>gaz_marsica</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Marsica</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>41.9706811718908</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>13.6367770065667</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4017,33 +4074,33 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>gaz_milano</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Milano</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>45.46417984291975</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>9.188743384040578</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4064,28 +4121,28 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>gaz_molise</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Molise</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>41.667749</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>14.573358</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4106,33 +4163,33 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>gaz_molo_beverello</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Molo Beverello</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Molo del Porto di Napoli</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>40.83845747697102</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>14.25512089831604</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4153,33 +4210,33 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>gaz_monte_algido</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Monte Algido</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Colli Albani</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>41.75024597370798</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>12.774504127034607</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4200,33 +4257,33 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>gaz_monte_cengio</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Monte Cengio</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Monte dell'Altipiano Veneto</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>45.83464690564686</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>11.395</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4247,28 +4304,28 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>gaz_monte_circeo</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Monte Circeo</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>41.25277506832153</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>13.056903290988464</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4289,28 +4346,28 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>gaz_monte_manno</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Monte Manno</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>41.70507314535531</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>12.933066487462336</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4331,33 +4388,33 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>gaz_monte_matese</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Monte Matese</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Monte del Molise</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>41.451044369853264</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>14.366554255055233</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4378,28 +4435,28 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>gaz_monte_soratte</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Monte Soratte</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>42.27001081429104</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>12.490957672092293</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4420,33 +4477,33 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>gaz_monte_velino</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Monte Velino</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Monte tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>42.165421795541896</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>13.388224454942325</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4467,28 +4524,28 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>gaz_monteleone</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Monteleone Sabino</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>42.232609158947405</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>12.859136459324375</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4509,33 +4566,33 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>gaz_monti</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Monti</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Quartiere di Roma</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>41.89481897366331</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>12.49251620797544</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4556,33 +4613,33 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>gaz_monti_carseolani</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Monti Carseolani</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Catena montuosa tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>42.0749429984885</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>13.032114125147414</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4603,33 +4660,33 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>gaz_monti_ernici</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Monti Ernici</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Catena montuosa tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>41.81035580365862</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>13.48593067326618</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4650,33 +4707,33 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>gaz_monti_simbruini</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Monti Simbruini</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Catena montuosa tra Lazio e Abruzzo</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>41.79718465634362</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>13.644952964344878</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4697,33 +4754,33 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>gaz_ostia</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Ostia</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>41.73245855250897</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>12.278829513185713</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4744,33 +4801,33 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>gaz_ovindoli</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Ovindoli</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Comune</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>42.13780481791833</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>13.51516522684632</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4791,28 +4848,28 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>gaz_padova</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>45.40750149300311</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>11.873753041768424</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4833,38 +4890,38 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>gaz_palazzo</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Palazzo</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Palazzo Morgana</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>00134 Stazione di Pavona-palazzo Morgana</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>41.71799629809183</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>12.597231861624314</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4885,33 +4942,33 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>gaz_palazzo_chigi</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Palazzo Chigi</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>P.za Colonna, 391, 00186</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>41.90123174971493</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>12.47981741059732</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4932,28 +4989,28 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>gaz_palazzo_della_immacolatella</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Palazzo della Immacolatella</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>40.84161917254697</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>14.258960456507776</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -4974,33 +5031,33 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>gaz_palazzo_pio</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Palazzo Pio</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Piazza del Biscione</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>41.89533742794816</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>12.473007850337243</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5021,33 +5078,33 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>gaz_palazzo_ruspoli</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Palazzo Ruspoli</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Via della Fontanella di Borghese, 56, 00186 Roma RM</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>41.904291483212205</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>12.47872570766404</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5068,33 +5125,33 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>gaz_palazzo_odescalchi_simonetti</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Palazzo Odescalchi Simonetti</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Via Vittoria Colonna, 13, 00193</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>41.90520237070184</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>12.472392994101876</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5114,44 +5171,44 @@
 }</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>Candidato della lettura di Terzoli (cit. in Pinotti 2025, p. 78): palazzo Odescalchi Simonetti, già pensione White, dove Gadda aveva abitato. Civico 11 secondo Pinotti; il dato precedente indicava 13. Non è il referente di palazzo_simonetti: entità predisposta per l'identificazione attribuita.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>gaz_palazzo_venezia</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Palazzo Venezia</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Palazzo del Mappamondo</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Piazza di Venezia, 3, 00186 Roma RM</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>41.89608880158758</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>12.482488256557962</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5172,28 +5229,28 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>gaz_palestrina</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Palestrina</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>41.83422291934301</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>12.888132917750513</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5214,38 +5271,38 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>gaz_pantheon</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Pantheon</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Terme di Agrippa</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Piazza della Rotonda, 00186</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>41.89867683406545</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>12.476863407009992</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5266,33 +5323,33 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>gaz_pavona</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Pavona</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Pavona</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>41.72553775484286</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>12.61219280831608</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5313,33 +5370,33 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>gaz_piazza_colonna</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Piazza Colonna</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Piazza Colonna</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>41.90088848088894</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>12.47993539405843</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5360,33 +5417,33 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>gaz_piazza_di_pietra</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Piazza di Pietra</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Piazza di Pietra</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>41.89999819105845</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>12.479385384272035</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5407,33 +5464,33 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>gaz_piazza_di_spagna</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Piazza di Spagna</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Piazza di Spagna</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>41.90571279324034</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>12.482325564335817</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5454,38 +5511,38 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>gaz_piazza_esedra</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Piazza Esedra</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>Piazza della Repubblica</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Piazza Esedra</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>41.902472842408514</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>12.496321983673056</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5506,33 +5563,33 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>gaz_piazza_garibaldi</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Piazza Garibaldi</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Piazzale Giuseppe Garibaldi</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>41.89198953301559</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>12.460553558380496</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5553,38 +5610,38 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>gaz_piazza_montanara</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Piazza Montanara</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>Piazza Montanara</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>demolita nel 1934</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>41.89249955749</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>12.480250892538322</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5605,33 +5662,33 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>gaz_piazza_pollarola</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>Piazza Pollarola</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Piazza Pollarola</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>41.895990126304326</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>12.472928812263008</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5652,38 +5709,38 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>gaz_piazza_rusticucci</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Piazza Rusticucci</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>Piazza Rusticucci (demolita nel 1940)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Piazza Pio XII</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>41.90257061274494</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>12.45975825285214</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5704,33 +5761,33 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>gaz_piazza_san_giovanni</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Piazza San Giovanni</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Piazza San Giovanni in Laterano</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>41.88742084063378</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>12.506173147859243</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5751,33 +5808,33 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>gaz_piazza_san_lorenzo_in_lucina</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Piazza San Lorenzo in Lucina</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Piazza San Lorenzo in Lucina</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>41.90361766730038</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>12.47842775822113</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5798,33 +5855,33 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>gaz_piazza_san_pietro</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Piazza San Pietro</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Piazza San Pietro</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>41.9022608794283</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>12.457233173334089</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5845,33 +5902,33 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>gaz_piazza_verdi</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Piazza Verdi</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Piazza Giuseppe Verdi</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>41.919679006917015</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>12.495028075136045</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5892,33 +5949,33 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>gaz_piazza_vittorio_emanuele</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Piazza Vittorio Emanuele</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Piazza Vittorio Emanuele II</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>41.895124393144</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>12.5048427733034</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5939,28 +5996,28 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>gaz_piceno</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Piceno</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>42.85363261520004</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>13.567540016779384</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -5981,33 +6038,33 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>gaz_pincio</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>Pincio</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Colle del Pincio</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>41.9115148827888</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>12.479706623913264</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6028,38 +6085,38 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>gaz_policlinico</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Policlinico</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>Policlinico Umberto I</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Via Giovanni Maria Lancisi, 2, 00161</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>41.90863414049968</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>12.50917293969651</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6080,28 +6137,28 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>gaz_ponte_divino_amore</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Ponte al Divino Amore</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>41.76071420037528</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>12.599632278065911</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6122,38 +6179,38 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>gaz_porta_angelica</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Porta Angelica</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Porta Angelica</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>demolita nel 1888</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>41.90616185465161</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>12.456647366153756</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6174,33 +6231,33 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>gaz_porta_latina</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Porta Latina</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Mura aureliane, Via di Porta Latina, 14, 00179 Roma RM</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>41.8782334566828</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>12.499128817987987</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6221,33 +6278,33 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>gaz_porta_maggiore</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Porta Maggiore</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Piazza di Porta Maggiore, 00182 Roma RM</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>41.89143521467929</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>12.51518714724432</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6268,33 +6325,33 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>gaz_porta_pinciana</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Porta Pinciana</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Via Vittorio Veneto, 196, 00187</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>41.90968492139161</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>12.488262466067692</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6315,28 +6372,28 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>gaz_porta_san_paolo</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Porta San Paolo</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>41.87683414708175</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>12.481441271164153</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6357,33 +6414,33 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>gaz_pozzo_delle_cornacchie</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Pozzo delle Cornacchie</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>via del Pozzo delle Cornacchie</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>41.900132740766</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>12.476009448493592</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6404,33 +6461,33 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>gaz_prati</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Prati</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Rione XXII</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>41.90875142605531</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>12.465194747823828</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6451,28 +6508,28 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>gaz_prati_di_castello</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Prati di Castello</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>41.90963380954534</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>12.4651701137127</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6493,33 +6550,33 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>gaz_pratica_di_mare</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Pratica di Mare</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Pratica di Mare</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>41.66401971901388</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>12.479969808767637</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6540,28 +6597,28 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>gaz_predappio</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Predappio</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>44.10833194442195</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>11.981884102223214</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6582,38 +6639,38 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>gaz_publicii_clivio_de</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Publicii clivio de'</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>(clivio de')</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Clivio dei Publicii</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>41.88571995557534</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>12.48263328901126</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6634,28 +6691,28 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Quarto di Santa Fumia</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>41.73247489501876</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>12.58446168893847</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6676,33 +6733,33 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>gaz_quattro_cantoni</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Quattro Cantoni</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>via dei Quattro Cantoni, 00184</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>41.8964282361213</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>12.496553006621577</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6723,28 +6780,28 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>gaz_reggio_calabria</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Reggio Calabria</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>38.12747821699881</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>15.652447605612965</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6765,38 +6822,38 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>gaz_regina_coeli</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Regina Coeli</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>gaz_lungara</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Via della Lungara, 29, 00165</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>41.89541963959722</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>12.463486619911356</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6817,33 +6874,33 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>gaz_ripetta</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Ripetta</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Passeggiata di Ripetta</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>41.90910697941768</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>12.474356718309616</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6864,28 +6921,28 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>gaz_rocca_di_papa</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Rocca di Papa</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>41.76238950891051</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>12.706774730883602</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6906,28 +6963,28 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>gaz_rocca_orsina</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Rocca Orsina</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>41.76991636096222</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>12.658476221527655</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6948,33 +7005,33 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>gaz_rocca_savella</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Rocca Savella</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>clivo di Rocca Savella</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>41.88624438963685</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>12.48057907706965</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -6995,28 +7052,28 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>gaz_roma</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Roma</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>41.89712290196547</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>12.483780073676602</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7037,33 +7094,33 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>gaz_sacro_cuore</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Sacro Cuore</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>Via Marsala, 42, 00185</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>41.90255587411117</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>12.502382758820149</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7084,28 +7141,28 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>gaz_salsomaggiore</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Salsomaggiore</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>44.81905616432461</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>9.979392469787877</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7126,33 +7183,33 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>gaz_san_callisto</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>San Callisto</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Via Appia Antica, 110/126, 00179</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>41.85910305676804</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>12.510725763767082</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7173,38 +7230,38 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>gaz_san_camillo</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>San Camillo</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Ospedale Vannini dell'Istituto delle figlie di san Camillo</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Circonvallazione Gianicolense, 87, 00149</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>41.86966525125673</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>12.456303092017317</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7225,33 +7282,33 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>gaz_san_carlo_alle_quattro_fontane</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>San Carlo alle quattro fontane</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Via del Quirinale, 23, 00187</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>41.901863522116905</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>12.490746406108268</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7272,33 +7329,33 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>gaz_san_clemente</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>San Clemente</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Piazza di S. Clemente, 00184</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>41.88952632925135</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>12.497564978356351</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7319,38 +7376,38 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>gaz_san_giovanni</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>San Giovanni</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Commissariato di P.S. San Giovanni</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>via Casalmonferrato 25 00182, Roma</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>41.88075040110243</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>12.51886092484358</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7371,38 +7428,38 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>gaz_san_giovanni_in_laterano</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>San Giovanni in Laterano</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Galilei</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>P.za. San Giovanni In Laterano, 00184</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>41.88599013299084</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>12.50562195401995</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7423,38 +7480,38 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>gaz_san_lorenzo_al_verano</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>San Lorenzo al verano</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>San Lorenzo fuori le Mura</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Piazzale del Verano, 3, 00185</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>41.90261005150349</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>12.520581205893716</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7475,33 +7532,33 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>gaz_san_luigi_de_francesi</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>San Luigi de' Francesi</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Piazza di S. Luigi de' Francesi, 00186</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>41.899621753079465</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>12.47471902436365</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7522,33 +7579,33 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>gaz_san_martino_ai_monti</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>San Martino ai Monti</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Vle del Monte Oppio, 28, 00184</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>41.894677226531456</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>12.498384893656386</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7569,28 +7626,28 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>gaz_san_silvestro_in_capite</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>San Silvestro in Capite</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>41.90289491613001</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>12.4807727698506</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7611,28 +7668,28 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>gaz_sannio</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>Sannio</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>41.260503</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>14.740775</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7653,33 +7710,33 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>gaz_santa_chiara</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Santa Chiara</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>P.za di S. Chiara, 14, 00186</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>41.89767270494693</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>12.4766157816818</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7700,33 +7757,33 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>gaz_santa_croce_in_gerusalemme</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Santa Croce in Gerusalemme</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Piazza di S. Croce in Gerusalemme, 10, 00185</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>41.88898866930153</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>12.514682435189837</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7747,38 +7804,38 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>gaz_santa_margherita_in_abitacolo</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Santa Margherita in Abitacolo</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Santa Rita Invitàcolo</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Via Montanara, 00186</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>41.89267907132654</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>12.480113538487586</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7799,38 +7856,38 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>gaz_santa_maria_della_neve</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Santa Maria della Neve</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Santa Maria Maggiore</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Via del Colosseo, 19, 00184</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>41.89269599966251</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>12.490115463118764</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7851,33 +7908,33 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>gaz_santa_maria_in_aquiro</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Santa Maria in Aquiro</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>Piazza Capranica, 00186</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>41.90014365391151</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>12.477999492672676</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7898,33 +7955,33 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>gaz_santa_maria_in_domnica</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Santa Maria in Dòmnica</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Via della Navicella, 10, 00184</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>41.88479505138305</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>12.495713660513266</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7945,33 +8002,33 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>gaz_santa_maria_in_porta_paradisi</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Santa Maria in Porta Paradisi</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Via di Ripetta, 61, 00186</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>41.90753807576588</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>12.475955971957005</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -7992,38 +8049,38 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>gaz_santa_maria_maggiore</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Santa Maria Maggiore</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Santa Maria della Neve</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>P.za di Santa Maria Maggiore, 00100</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>41.89783811990252</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>12.498397680304144</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8044,28 +8101,28 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>gaz_santa_maria_novella</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Santa Maria Novella</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>43.77709097635588</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>11.248280584031749</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8086,28 +8143,28 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>gaz_santa_maria_sopra_minerva</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Santa Maria sopra Minerva</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>41.89799121298735</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>12.477810026767758</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I167" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8128,33 +8185,33 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>gaz_santa_palomba</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Santa Palomba</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Via della Stazione, 00040</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>41.70649880109798</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H168" t="inlineStr">
         <is>
           <t>12.573826656277753</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I168" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8175,38 +8232,38 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>gaz_santa_rita_invitacolo</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Santa Rita Invitàcolo</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>Santa Margherita in Abitacolo</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Via Montanara, 00186</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>41.89267907132654</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>12.480113538487586</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8227,33 +8284,33 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>gaz_santagnese_in_agone</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Sant'Agnese in Agone</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Via di Santa Maria dell'Anima, 30/A, 00186</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>41.89886028109439</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H170" t="inlineStr">
         <is>
           <t>12.472549957571031</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8274,33 +8331,33 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>gaz_santagostino</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Sant'Agostino</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>P.za di S. Agostino, 00186</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>41.9008508106466</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>12.474278565476274</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I171" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8321,33 +8378,33 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>gaz_santandrea_della_valle</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Sant'Andrea della Valle</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Corso Vittorio Emanuele II, 00186</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>41.89641220677437</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>12.474333258746212</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8368,33 +8425,33 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>gaz_santanna</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Sant'Anna</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Via Sant'Anna, 00120</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>41.90407297051054</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>12.457481602903693</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8415,33 +8472,33 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>gaz_santantonio_da_padova</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Sant'Antonio da Padova</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>Via Merulana, 124, 00185</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>41.88896555883594</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>12.50405706965514</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8462,33 +8519,33 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>gaz_santi_quattro_coronati</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Santi Quattro Coronati</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Via dei SS. Quattro, 20, 00184</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>41.88828469760136</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>12.498505681387911</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I175" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8509,38 +8566,38 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>gaz_santo_stefano_del_cacco_celio_santo_stefano</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Santo Stefano del Cacco, Celio-Santo Stefano</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>gaz_collegio_romano</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>via Santo Stefano del Cacco</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>41.89737347768524</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H176" t="inlineStr">
         <is>
           <t>12.47948307900791</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I176" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8561,33 +8618,33 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>gaz_santo_stefano_rotondo</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Santo Stefano Rotondo</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Via Santo Stefano Rotondo, 7, 00184</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>41.885983052252186</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>12.499315306942016</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I177" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8608,28 +8665,28 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>gaz_sardegna</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Sardegna</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>40.23470155220895</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>9.054925146792344</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8650,28 +8707,28 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>gaz_sassari</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Sassari</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>40.72924779449954</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>8.55541661770075</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I179" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8692,38 +8749,38 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>gaz_solforata</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Solforata</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Solfarata, Solfatara</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Solfarata</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>41.70161467494166</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>12.538157750574666</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I180" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8744,28 +8801,28 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>gaz_soriano_nel_cimino</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Soriano nel Cimino</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>42.43655912777748</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>12.235774006217756</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I181" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8786,33 +8843,33 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>gaz_suburra</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Suburra</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Suburra, Roma</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>41.89676284011875</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="H182" t="inlineStr">
         <is>
           <t>12.49666104629743</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="I182" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8833,38 +8890,38 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>gaz_teatro_jovinelli</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Teatro Jovinelli</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>Ambra Jovinelli</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>Via Guglielmo Pepe, 45, 00185</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>41.89552360992579</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H183" t="inlineStr">
         <is>
           <t>12.508280896240649</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I183" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8885,38 +8942,38 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>gaz_tempio_di_agrippa</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Tempio di Agrippa</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>Pantheon</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Piazza della Rotonda, 00186</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>41.89867683406545</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>12.476863407009992</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I184" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8937,33 +8994,33 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>gaz_terme_di_caracalla</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Terme di Caracalla</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Viale delle Terme di Caracalla, 00153</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>41.87937370424267</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>12.492407213493443</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I185" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -8984,33 +9041,33 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>gaz_termini</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Termini</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Via Giovanni Giolitti, 40, 00185</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>41.90058242591175</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="H186" t="inlineStr">
         <is>
           <t>12.502530478441573</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I186" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9031,33 +9088,33 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>gaz_terracina</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Terracina</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Comune</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>41.29047601665066</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>13.249936342430493</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I187" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9078,33 +9135,33 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>gaz_tevere</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Tevere</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Fiume</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>41.89465722886191</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
+      <c r="H188" t="inlineStr">
         <is>
           <t>12.467929197570816</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I188" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9125,28 +9182,28 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>gaz_tivoli</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Tivoli</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="G189" t="inlineStr">
         <is>
           <t>41.95975597738329</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="H189" t="inlineStr">
         <is>
           <t>12.802413747816448</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="I189" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9167,43 +9224,43 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>gaz_tor_ser_paolo</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Tor Ser Paolo</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>Torre Messer Paoli</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>Tor Ser Paolo</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Ciampino (Colli Albani)</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>41.77489532732517</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
+      <c r="H190" t="inlineStr">
         <is>
           <t>12.626476138456598</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="I190" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9224,33 +9281,33 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>gaz_torraccio</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>Torraccio</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>Frazione di Marino</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>41.760346741901486</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
+      <c r="H191" t="inlineStr">
         <is>
           <t>12.623648121781372</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I191" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9271,33 +9328,33 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>gaz_traforo</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>Traforo</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>Traforo Umberto I</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>41.90087528377779</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
+      <c r="H192" t="inlineStr">
         <is>
           <t>12.48796567063664</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
+      <c r="I192" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9318,28 +9375,28 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>gaz_trastevere</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>Trastevere</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>41.88539020297163</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H193" t="inlineStr">
         <is>
           <t>12.47032722280828</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
+      <c r="I193" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9360,33 +9417,33 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>gaz_tranvie_dei_castelli</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>Tranvie dei Castelli</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>Tramvie dei Castelli</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>41.87842995242856</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H194" t="inlineStr">
         <is>
           <t>12.518773149025854</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I194" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9407,33 +9464,33 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>gaz_vado_ligure</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Vado Ligure</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>44.27104046105365</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H195" t="inlineStr">
         <is>
           <t>8.43855565508531</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I195" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9454,33 +9511,33 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>gaz_valle_fondo</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>Valle Fondo</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Località</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G196" t="inlineStr">
         <is>
           <t>41.72754639015884</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="H196" t="inlineStr">
         <is>
           <t>12.649994748861523</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I196" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9501,33 +9558,33 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>gaz_velletri</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>Velletri</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>Comune</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>41.68473269013517</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
+      <c r="H197" t="inlineStr">
         <is>
           <t>12.777920637406812</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I197" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9548,33 +9605,33 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>gaz_verona</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>45.44286986165943</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="H198" t="inlineStr">
         <is>
           <t>10.998439464162914</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I198" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9595,33 +9652,33 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>gaz_via_anziate</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Via Anziate</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Anziatina, Nettunense</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>41.91177548861766</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
+      <c r="H199" t="inlineStr">
         <is>
           <t>12.442903033569449</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
+      <c r="I199" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9642,28 +9699,28 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>gaz_via_appia</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Via Appia</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>41.85054042792461</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
+      <c r="H200" t="inlineStr">
         <is>
           <t>12.52314794887518</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I200" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9684,28 +9741,28 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>gaz_via_ardeatina</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>Via Ardeatina</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G201" t="inlineStr">
         <is>
           <t>41.748548036845285</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
+      <c r="H201" t="inlineStr">
         <is>
           <t>12.560749021883575</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
+      <c r="I201" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9726,28 +9783,28 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>gaz_via_boncompagni</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>Via Boncompagni</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>41.908587241676514</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
+      <c r="H202" t="inlineStr">
         <is>
           <t>12.49349032119079</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I202" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9768,33 +9825,33 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>gaz_via_botteghe_oscure</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>Via Botteghe Oscure</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>via delle Botteghe Oscure</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>41.89509493955358</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H203" t="inlineStr">
         <is>
           <t>12.478981335522056</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I203" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9815,33 +9872,33 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>gaz_via_campo_marzio</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Via Campo Marzio</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>via di Campo Marzio</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>41.90233603425503</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
+      <c r="H204" t="inlineStr">
         <is>
           <t>12.477565835193412</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I204" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9862,28 +9919,28 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>gaz_via_capo_dafrica</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Via Capo d'Africa</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>41.888955504808656</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H205" t="inlineStr">
         <is>
           <t>12.495370807914474</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I205" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9904,28 +9961,28 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>gaz_via_carlo_alberto</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Via Carlo Alberto</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>41.89631462157369</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H206" t="inlineStr">
         <is>
           <t>12.501608522565736</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I206" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9946,28 +10003,28 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>gaz_via_colonna_vittoria</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Via Colonna Vittoria</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>41.90532009591583</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H207" t="inlineStr">
         <is>
           <t>12.472080293657111</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I207" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -9988,28 +10045,28 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>gaz_via_dazeglio</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>Via D'Azeglio</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>41.9005646386736</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H208" t="inlineStr">
         <is>
           <t>12.497986264095715</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I208" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10030,28 +10087,28 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>gaz_via_de_merli</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>Via de' Merli</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>41.8919173419505</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H209" t="inlineStr">
         <is>
           <t>12.50204620435122</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I209" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10072,28 +10129,28 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>gaz_via_de_querceti</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Via de' Querceti</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>41.88826403566792</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>12.497769533571477</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I210" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10114,28 +10171,28 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>gaz_via_degli_zingari</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>Via degli Zingari</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>41.8953237669349</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>12.491807177069209</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I211" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10156,28 +10213,28 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>gaz_via_dei_banchi_vecchi</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>Via dei Banchi Vecchi</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>41.89855410311026</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H212" t="inlineStr">
         <is>
           <t>12.466855862738894</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I212" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10198,28 +10255,28 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>gaz_via_dei_capocci</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Via dei Capocci</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>41.89635704216215</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="H213" t="inlineStr">
         <is>
           <t>12.493746031107008</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
+      <c r="I213" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10240,28 +10297,28 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>gaz_via_dei_fienili</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Via dei Fienili</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>41.89082656400838</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
+      <c r="H214" t="inlineStr">
         <is>
           <t>12.48348109299745</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
+      <c r="I214" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10282,28 +10339,28 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>gaz_via_dei_greci</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>Via dei Greci</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>41.907686875920895</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
+      <c r="H215" t="inlineStr">
         <is>
           <t>12.478760733837431</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
+      <c r="I215" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10324,28 +10381,28 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>gaz_via_dei_serpenti</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>Via dei Serpenti</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>41.89625372175469</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
+      <c r="H216" t="inlineStr">
         <is>
           <t>12.490298122566564</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
+      <c r="I216" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10366,28 +10423,28 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>gaz_via_del_corso</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Via del Corso</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G217" t="inlineStr">
         <is>
           <t>41.90038661195777</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
+      <c r="H217" t="inlineStr">
         <is>
           <t>12.480692510904577</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
+      <c r="I217" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10408,28 +10465,28 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>gaz_via_del_gesu</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>Via del Gesù</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>41.8967983204413</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H218" t="inlineStr">
         <is>
           <t>12.478768993659564</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I218" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10450,33 +10507,33 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>gaz_via_del_gobbo</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Via del Gobbo</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>Via Aurelio del Gobbo</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G219" t="inlineStr">
         <is>
           <t>41.77631176902448</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="H219" t="inlineStr">
         <is>
           <t>12.67390716539034</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I219" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10497,28 +10554,28 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>gaz_via_del_parlamento</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Via del Parlamento</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G220" t="inlineStr">
         <is>
           <t>41.90266671761795</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H220" t="inlineStr">
         <is>
           <t>12.479531435421766</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I220" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10539,28 +10596,28 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>gaz_via_della_caffarella</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Via della Caffarella</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>41.86491462396609</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H221" t="inlineStr">
         <is>
           <t>12.51298416209954</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="I221" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10581,28 +10638,28 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>gaz_via_della_falcognana</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Via della Falcognana</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G222" t="inlineStr">
         <is>
           <t>41.75989937203588</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H222" t="inlineStr">
         <is>
           <t>12.58052436788742</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I222" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10623,28 +10680,28 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>gaz_via_della_navicella</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>Via della Navicella</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>41.883995357992056</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="H223" t="inlineStr">
         <is>
           <t>12.496271259883107</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="I223" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10665,28 +10722,28 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>gaz_via_della_palombella</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>Via della Palombella</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G224" t="inlineStr">
         <is>
           <t>41.89835257325988</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H224" t="inlineStr">
         <is>
           <t>12.476684905643626</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I224" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10707,28 +10764,28 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>gaz_via_della_scrofa</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>Via della Scrofa</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G225" t="inlineStr">
         <is>
           <t>41.89999474967304</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
+      <c r="H225" t="inlineStr">
         <is>
           <t>12.477970515691876</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
+      <c r="I225" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10749,28 +10806,28 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>gaz_via_della_vite</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>Via della Vite</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G226" t="inlineStr">
         <is>
           <t>41.90388247365601</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="H226" t="inlineStr">
         <is>
           <t>12.481236040688875</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
+      <c r="I226" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10791,28 +10848,28 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>gaz_via_delle_coppelle</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>Via delle Coppelle</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G227" t="inlineStr">
         <is>
           <t>41.900528326072674</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
+      <c r="H227" t="inlineStr">
         <is>
           <t>12.475815197103683</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
+      <c r="I227" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10833,33 +10890,33 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>gaz_via_di_ferro</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>Via di Ferro</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>via Capo di Ferro</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G228" t="inlineStr">
         <is>
           <t>41.89411186215077</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>12.47225542803289</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
+      <c r="I228" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10880,28 +10937,28 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>gaz_via_di_grotta_pinta</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>Via di Grotta Pinta</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G229" t="inlineStr">
         <is>
           <t>41.895285483518485</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
+      <c r="H229" t="inlineStr">
         <is>
           <t>12.473999194642012</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
+      <c r="I229" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10922,28 +10979,28 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>gaz_via_di_pietra</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>Via di Pietra</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>41.90017316845467</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>12.480302763446346</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
+      <c r="I230" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -10964,28 +11021,28 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>gaz_via_di_san_paolo_della_croce</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>Via di San Paolo della Croce</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G231" t="inlineStr">
         <is>
           <t>41.88609007715952</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="H231" t="inlineStr">
         <is>
           <t>12.494225506290569</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
+      <c r="I231" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11006,28 +11063,28 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>gaz_via_di_santo_stefano_rotondo</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>Via di Santo Stefano Rotondo</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G232" t="inlineStr">
         <is>
           <t>41.8859031777105</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
+      <c r="H232" t="inlineStr">
         <is>
           <t>12.49934749037454</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="I232" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11048,28 +11105,28 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>gaz_via_frangipane</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>Via Frangipane</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>41.89345109820309</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H233" t="inlineStr">
         <is>
           <t>12.490184834220564</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I233" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11090,38 +11147,38 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>gaz_via_labbricana</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>Via Labbricana</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>via Labicana</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>via Labicana</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G234" t="inlineStr">
         <is>
           <t>41.88997394077698</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
+      <c r="H234" t="inlineStr">
         <is>
           <t>12.498761606943075</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
+      <c r="I234" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11142,33 +11199,33 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>gaz_via_lanza</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>Via Lanza</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>via Giovanni Lanza</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>41.8952468123314</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
+      <c r="H235" t="inlineStr">
         <is>
           <t>12.496558649455126</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="I235" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11189,28 +11246,28 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>gaz_via_ludovisi</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>Via Ludovisi</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G236" t="inlineStr">
         <is>
           <t>41.907046946215466</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
+      <c r="H236" t="inlineStr">
         <is>
           <t>12.487880279008024</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="I236" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11231,28 +11288,28 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>gaz_via_mamiani</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>Via Mamiani</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G237" t="inlineStr">
         <is>
           <t>41.8962647321153</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
+      <c r="H237" t="inlineStr">
         <is>
           <t>12.505176649501491</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="I237" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11273,28 +11330,28 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>gaz_via_massimo_dazeglio</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>Via Massimo d'Azeglio</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G238" t="inlineStr">
         <is>
           <t>41.7708010201672</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
+      <c r="H238" t="inlineStr">
         <is>
           <t>12.656666611845928</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
+      <c r="I238" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11315,28 +11372,28 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>gaz_via_merulana</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>Via Merulana</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G239" t="inlineStr">
         <is>
           <t>41.8919173419505</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
+      <c r="H239" t="inlineStr">
         <is>
           <t>12.50204620435122</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
+      <c r="I239" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11357,28 +11414,28 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>gaz_via_milano</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>Via Milano</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G240" t="inlineStr">
         <is>
           <t>41.89826988439785</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
+      <c r="H240" t="inlineStr">
         <is>
           <t>12.490991532899102</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="I240" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11399,33 +11456,33 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>gaz_via_monte_caprino</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>Via Monte Caprino</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>via di Monte Caprino</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G241" t="inlineStr">
         <is>
           <t>41.8915647770543</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
+      <c r="H241" t="inlineStr">
         <is>
           <t>12.481163670442754</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
+      <c r="I241" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11446,28 +11503,28 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>gaz_via_montebello</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>Via Montebello</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>41.90645672391186</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
+      <c r="H242" t="inlineStr">
         <is>
           <t>12.501167377390898</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
+      <c r="I242" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11488,28 +11545,28 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>gaz_via_nicotera</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>Via Nicotera</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G243" t="inlineStr">
         <is>
           <t>41.91624918540069</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
+      <c r="H243" t="inlineStr">
         <is>
           <t>12.468244588924025</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
+      <c r="I243" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11530,28 +11587,28 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>gaz_via_orazio</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>Via Orazio</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G244" t="inlineStr">
         <is>
           <t>41.9159462938855</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
+      <c r="H244" t="inlineStr">
         <is>
           <t>12.468458865543028</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
+      <c r="I244" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11572,28 +11629,28 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>gaz_via_panisperna</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>Via Panisperna</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="G245" t="inlineStr">
         <is>
           <t>41.89663706340232</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
+      <c r="H245" t="inlineStr">
         <is>
           <t>12.491129905973104</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
+      <c r="I245" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11614,33 +11671,33 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>gaz_via_popolonia</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>Via Popolonia</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>Via populonia</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G246" t="inlineStr">
         <is>
           <t>41.8764745142944</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
+      <c r="H246" t="inlineStr">
         <is>
           <t>12.50579364816932</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
+      <c r="I246" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11661,28 +11718,28 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>gaz_via_ricasoli</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>Via Ricasoli</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G247" t="inlineStr">
         <is>
           <t>41.89558786458463</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
+      <c r="H247" t="inlineStr">
         <is>
           <t>12.50606607937935</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
+      <c r="I247" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11703,28 +11760,28 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>gaz_via_valadier</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>Via Valadier</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G248" t="inlineStr">
         <is>
           <t>41.90825496417197</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>12.469020520920948</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
+      <c r="I248" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11745,28 +11802,28 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>gaz_via_veneto</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>Via Veneto</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="G249" t="inlineStr">
         <is>
           <t>41.906261368657</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H249" t="inlineStr">
         <is>
           <t>12.48958462091846</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
+      <c r="I249" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11787,28 +11844,28 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>gaz_via_venti_settembre</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>Via Venti Settembre</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G250" t="inlineStr">
         <is>
           <t>41.90577385586054</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
+      <c r="H250" t="inlineStr">
         <is>
           <t>12.496004176747949</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
+      <c r="I250" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11829,28 +11886,28 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>gaz_via_villari</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>Via Vìllari</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G251" t="inlineStr">
         <is>
           <t>41.88999351453406</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
+      <c r="H251" t="inlineStr">
         <is>
           <t>12.502061807590628</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
+      <c r="I251" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11871,28 +11928,28 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>gaz_via_zanardelli</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>Via Zanardelli</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G252" t="inlineStr">
         <is>
           <t>41.9012714375299</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
+      <c r="H252" t="inlineStr">
         <is>
           <t>12.472265477389731</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
+      <c r="I252" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11913,38 +11970,38 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>gaz_viale_della_regina</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>Viale della Regina</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>vedi anche Viale Regina Margherita</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>viale Regina Margherita</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>41.914435250731664</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
+      <c r="H253" t="inlineStr">
         <is>
           <t>12.505081063122308</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
+      <c r="I253" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -11965,28 +12022,28 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>gaz_viale_liegi</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>Viale Liegi</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="G254" t="inlineStr">
         <is>
           <t>41.92139386789227</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
+      <c r="H254" t="inlineStr">
         <is>
           <t>12.495723748817309</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr">
+      <c r="I254" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12007,33 +12064,33 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>gaz_viale_regina_margherita</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Viale Regina Margherita</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>vedi anche Viale della Regina</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
+      <c r="G255" t="inlineStr">
         <is>
           <t>41.914435250731664</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H255" t="inlineStr">
         <is>
           <t>12.505081063122308</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
+      <c r="I255" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12054,33 +12111,33 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>gaz_vicenza</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Vicenza</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>Città</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G256" t="inlineStr">
         <is>
           <t>45.54782811997265</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
+      <c r="H256" t="inlineStr">
         <is>
           <t>11.54666863709906</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
+      <c r="I256" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12101,33 +12158,33 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>gaz_vicolo_ciancaleoni</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>Vicolo Ciancaleoni</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>vicolo de' Ciancaleoni</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
+      <c r="G257" t="inlineStr">
         <is>
           <t>41.89652544879445</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
+      <c r="H257" t="inlineStr">
         <is>
           <t>12.49319562190167</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr">
+      <c r="I257" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12148,33 +12205,33 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>gaz_vicolo_della_bucimazza</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Vicolo della Bucimazza</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
+      <c r="F258" t="inlineStr">
         <is>
           <t>via Bucimazza</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G258" t="inlineStr">
         <is>
           <t>41.89085398497711</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
+      <c r="H258" t="inlineStr">
         <is>
           <t>12.48282256606494</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
+      <c r="I258" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12195,28 +12252,28 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>gaz_vicolo_delle_grotte_del_teatro</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Vicolo delle Grotte del Teatro</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G259" t="inlineStr">
         <is>
           <t>41.89461101972113</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
+      <c r="H259" t="inlineStr">
         <is>
           <t>12.47247006996503</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
+      <c r="I259" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12237,28 +12294,28 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>gaz_villa_borghese</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Villa Borghese</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G260" t="inlineStr">
         <is>
           <t>41.91403582418124</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H260" t="inlineStr">
         <is>
           <t>12.485398757632616</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
+      <c r="I260" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12279,28 +12336,28 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>gaz_villa_celimontana</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Villa Celimontana</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G261" t="inlineStr">
         <is>
           <t>41.88404468598669</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H261" t="inlineStr">
         <is>
           <t>12.495211796641748</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
+      <c r="I261" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12321,28 +12378,28 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>gaz_villa_deste</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Villa d'Este</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G262" t="inlineStr">
         <is>
           <t>41.96358343762597</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H262" t="inlineStr">
         <is>
           <t>12.795864786733311</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
+      <c r="I262" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12363,28 +12420,28 @@
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>gaz_villa_gregoriana</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Villa Gregoriana</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G263" t="inlineStr">
         <is>
           <t>41.96553240632673</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H263" t="inlineStr">
         <is>
           <t>12.801778925481416</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
+      <c r="I263" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12405,28 +12462,28 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>gaz_viminale</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Viminale</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G264" t="inlineStr">
         <is>
           <t>41.89805973978667</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H264" t="inlineStr">
         <is>
           <t>12.494448968864743</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
+      <c r="I264" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12447,28 +12504,28 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>gaz_vinchiaturo</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>Vinchiaturo</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G265" t="inlineStr">
         <is>
           <t>41.49401046795862</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H265" t="inlineStr">
         <is>
           <t>14.587203598469978</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
+      <c r="I265" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12489,28 +12546,28 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>gaz_vomero</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>Vomero</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="G266" t="inlineStr">
         <is>
           <t>40.84468964152708</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
+      <c r="H266" t="inlineStr">
         <is>
           <t>14.23166148030254</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr">
+      <c r="I266" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",
@@ -12531,28 +12588,28 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>gaz_zagarolo</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>Zagarolo</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G267" t="inlineStr">
         <is>
           <t>41.839732856050645</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H267" t="inlineStr">
         <is>
           <t>12.829976839865571</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
+      <c r="I267" t="inlineStr">
         <is>
           <t>{
   "type": "FeatureCollection",

--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -1869,7 +1869,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Posizione ADOTTATA: TCI, Italia centrale I, carta «Colli Laziali, Monti Lepini ed Ernici» 1:250.000, inserita tra le pp. 480 e 481 (Manzotti 2010, Tav. VI, p. 300): casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato. Coordinate stimate (precisione ~1 km): punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia (OpenStreetMap). Posizione ALTERNATIVA: IGM, F. 150 III SO, 1:25.000, rilievo 1872, aggiornamenti 1931 e 1940 (Manzotti 2010, Tav. VII, p. 301): «Casale Abbruciato» a ovest della Roma–Napoli, stimato a 41.7168 N 12.5683 E (reticolo UTM 33 della tavola, E 297,7 N 4621,3 km; precisione ~250 m). Manzotti 2010, pp. 268–269. Nella nota Manzotti rinvia alle tavole come «V» e «VI»: qui si citano secondo le didascalie.</t>
+          <t>Posizione ADOTTATA: TCI, Italia centrale I, carta «Colli Laziali, Monti Lepini ed Ernici» 1:250.000, inserita tra le pp. 480 e 481 (Manzotti 2010, Tav. VI, p. 300): casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato. Coordinate stimate (precisione ~1 km): punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia (OpenStreetMap). Posizione ALTERNATIVA: IGM, F. 150 III SO, 1:25.000, rilievo 1872, aggiornamenti 1931 e 1940 (Manzotti 2010, Tav. VII, p. 301): «Casale Abbruciato» a ovest della Roma–Napoli, stimato a 41.7168 N 12.5683 E (reticolo UTM 33 della tavola, E 297,7 N 4621,3 km; precisione ~250 m; il reticolo della tavola è in datum ED50, e lo scarto verso WGS84, ~100–200 m, rientra in questa precisione). Manzotti 2010, pp. 268–269. Nella nota Manzotti rinvia alle tavole come «V» e «VI»: qui si citano secondo le didascalie.</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J267"/>
+  <dimension ref="A1:K267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>Authority_Source</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Housed_In</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1968,11 +1973,6 @@
           <t>Castel Gandolfo</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>gaz_castello</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>41.75005641875434</t>
@@ -2099,11 +2099,6 @@
           <t>Castello</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>gaz_castel_gandolfo</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>41.75143747946607</t>
@@ -2381,11 +2376,6 @@
           <t>Collegio Romano</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>gaz_santo_stefano_del_cacco_celio_santo_stefano</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>via Santo Stefano del Cacco</t>
@@ -3855,11 +3845,6 @@
           <t>Lungara</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>gaz_regina_coeli</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>via della Lungara</t>
@@ -6833,11 +6818,6 @@
           <t>Regina Coeli</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>gaz_lungara</t>
-        </is>
-      </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>Via della Lungara, 29, 00165</t>
@@ -6871,6 +6851,11 @@
     }
   ]
 }</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>gaz_lungara</t>
         </is>
       </c>
     </row>
@@ -8577,11 +8562,6 @@
           <t>Santo Stefano del Cacco, Celio-Santo Stefano</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>gaz_collegio_romano</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>via Santo Stefano del Cacco</t>
@@ -8615,6 +8595,11 @@
     }
   ]
 }</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>gaz_collegio_romano</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -1874,7 +1874,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Posizione ADOTTATA: TCI, Italia centrale I, carta «Colli Laziali, Monti Lepini ed Ernici» 1:250.000, inserita tra le pp. 480 e 481 (Manzotti 2010, Tav. VI, p. 300): casale fra le ferrovie Roma–Velletri e Roma–Napoli, all'altezza di Santa Fumia, lungo il fosso di Casale Abbrusciato. Coordinate stimate (precisione ~1 km): punto mediano fra le due ferrovie alla latitudine di Borgo Santa Fumia (OpenStreetMap). Posizione ALTERNATIVA: IGM, F. 150 III SO, 1:25.000, rilievo 1872, aggiornamenti 1931 e 1940 (Manzotti 2010, Tav. VII, p. 301): «Casale Abbruciato» a ovest della Roma–Napoli, stimato a 41.7168 N 12.5683 E (reticolo UTM 33 della tavola, E 297,7 N 4621,3 km; precisione ~250 m; il reticolo della tavola è in datum ED50, e lo scarto verso WGS84, ~100–200 m, rientra in questa precisione). Manzotti 2010, pp. 268–269. Nella nota Manzotti rinvia alle tavole come «V» e «VI»: qui si citano secondo le didascalie.</t>
+          <t>Posizioni attribuite: L-0001 (TCI, Italia centrale I, adottata) e L-0002 (IGM, F. 150 III SO, alternativa), lette da Manzotti 2010, pp. 268–269, Tavv. VI–VII (D-069).</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K266"/>
+  <dimension ref="A1:K270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12573,6 +12573,94 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>gaz_palazzo_colonna_marino</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Palazzo Colonna (Marino)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Palazzo Frangipani-Orsini-Colonna su piazza Umberto I, oggi piazza della Repubblica, a Marino</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Manzotti 2010, pp. 239–240 (TCI, Italia centrale IV, p. 761). Senza coordinate: bersaglio di una identificazione non adottata (I-0005, D-087).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>gaz_palazzo_de_carolis_simonetti</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Palazzo De Carolis Simonetti</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Via del Corso 307 / via Lata 3, Roma</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a, cit. in Terzoli 2015, p. 536; Pinotti 2025, p. 78. Senza coordinate: bersaglio di identificazioni non adottate (I-0007, I-0008, D-087).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>gaz_osteria_bivio_frattocchie</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Osteria al bivio (Frattocchie)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Osteria sul bivio fra Appia Antica e strada del Divino Amore, presso le Frattocchie</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Bertarelli 1925, cart. 1 («Osteria») e cart. 4 («Ost.»), secondo Terzoli 2015, p. 776. Senza coordinate: il luogo si posiziona dalle ancore (D-087).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>gaz_ponte_di_santa_fumia</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Ponte di Santa Fumia</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Ponte sulla ferrovia Roma–Velletri in località Santa Fumia</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Bertarelli 1925, cart. 4, secondo Terzoli 2015, pp. 418–419, 911. Senza coordinate; il luogo ponte_di_santa_fumia resta ancorato a gaz_quarto_di_santa_fumia (D-087).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/GazetteerEntities.xlsx
+++ b/data/source/xlsx/GazetteerEntities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K270"/>
+  <dimension ref="A1:K272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6947,6 +6947,11 @@
 }</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Terzoli 2015, pp. 507–508 (identificazione); coordinata nell'area di Palazzo Colonna, che occupa il sedime della rocca; coordinata verificata sul poligono OSM di Palazzo Colonna, way 74413768.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12658,6 +12663,85 @@
       <c r="J270" t="inlineStr">
         <is>
           <t>Bertarelli 1925, cart. 4, secondo Terzoli 2015, pp. 418–419, 911. Senza coordinate; il luogo ponte_di_santa_fumia resta ancorato a gaz_quarto_di_santa_fumia (D-087).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>gaz_via_delle_oche_milano</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>via delle Oche</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Via di Okk</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>contrada milanese scomparsa</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>via Bernardino Zenale, Milano, tra via San Vittore e corso Magenta, presso Santa Maria delle Grazie</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>45.464649</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>9.170031</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>{
+  "type": "FeatureCollection",
+  "features": [
+    {
+      "type": "Feature",
+      "properties": {},
+      "geometry": {
+        "type": "Point",
+        "coordinates": [
+          9.170031,
+          45.464649
+        ]
+      }
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Terzoli 2015, p. 77; L'Adalgisa, p. 564, n. 53. Coordinata: centroide di via Bernardino Zenale, OpenStreetMap, way 27756097 e 286239491.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>gaz_campidoglio</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Campidoglio</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Senza coordinate: bersaglio dell'identificazione non adottata I-0015 (Terzoli 2015, pp. 507–508).</t>
         </is>
       </c>
     </row>
